--- a/ИБ/5/Отчёт(FIN).xlsx
+++ b/ИБ/5/Отчёт(FIN).xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3B5275-C1EC-44E5-A94F-AAAD405119AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD63622-4E4B-4AB9-B0B3-25D9C7401031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2201,15 +2201,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>586740</xdr:colOff>
+      <xdr:colOff>375383</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>148590</xdr:rowOff>
+      <xdr:rowOff>131904</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>281940</xdr:colOff>
+      <xdr:colOff>70583</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>148590</xdr:rowOff>
+      <xdr:rowOff>131904</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
